--- a/tests/realSuite/Piano-Viaggi_Atletica-Ragazz-_8-maggio-2025_def_con-cell/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Atletica-Ragazz-_8-maggio-2025_def_con-cell/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,31 +631,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC FOLGARIA</t>
+          <t>IC CHIESE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fermata bus Palaghiaccio - Folgaria</t>
+          <t>Via Papaleoni 5 - Storo</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC FONDO-REVO'</t>
+          <t>IC FOLGARIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Park autobus c/o Vigili Fuoco Volontari - Revò</t>
+          <t>Fermata bus Palaghiaccio - Folgaria</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -666,7 +666,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SSPG - via G. Garibaldi, 24 - Fondo</t>
+          <t>Park autobus c/o Vigili Fuoco Volontari - Revò</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -676,91 +676,91 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC ISERA/ROVERETO</t>
+          <t>IC FONDO-REVO'</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Viale Vittoria 43 - Rovereto</t>
+          <t>SSPG - via G. Garibaldi, 24 - Fondo</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC LAVIS</t>
+          <t>IC ISERA/ROVERETO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SSPG - via Carlo Sette, 13/a - Lavis</t>
+          <t>Viale Vittoria 43 - Rovereto</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC LEVICO TERME</t>
+          <t>IC LAVIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SSPG – via della Pace, 5 - Levico Terme</t>
+          <t>SSPG - via Carlo Sette, 13/a - Lavis</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC MEZZANO SANTA CROCE</t>
+          <t>IC LEVICO TERME</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Via Molaren, 29 - Mezzano</t>
+          <t>SSPG – via della Pace, 5 - Levico Terme</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC MEZZOCORONA</t>
+          <t>IC MEZZANO SANTA CROCE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Via Fornai, 1 - Mezzocorona</t>
+          <t>Via Molaren, 29 - Mezzano</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC MEZZOCORONA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Via Trento Fermata bus - Spormaggiore</t>
+          <t>Via Fornai, 1 - Mezzocorona</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -771,37 +771,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Via degli Alpini, 17 - Mezzolombardo</t>
+          <t>Via Trento Fermata bus - Spormaggiore</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC PERGINE 1</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SSPG – Via Caduti, 39 - Pergine Valsugana</t>
+          <t>Via degli Alpini, 17 - Mezzolombardo</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC RIVA 1</t>
+          <t>IC PERGINE 1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SSPG - via D. Chiesa, 10 - Riva del Garda</t>
+          <t>SSPG – Via Caduti, 39 - Pergine Valsugana</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -811,12 +811,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IC RIVA 2</t>
+          <t>IC RIVA 1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Centro sportivo "Malossini" – Via Ginestre 1 - Riva del Garda</t>
+          <t>SSPG - via D. Chiesa, 10 - Riva del Garda</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -826,16 +826,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC RIVA 2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Piazza della Chiesa - Coredo</t>
+          <t>Centro sportivo "Malossini" – Via Ginestre 1 - Riva del Garda</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -846,97 +846,97 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Piazza della Chiesa – Taio</t>
+          <t>Piazza della Chiesa - Coredo</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC TAIO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SSPG – via Circonvallazione, 44 – Tione</t>
+          <t>Piazza della Chiesa – Taio</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IC TRENTO 1</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SSPG - via Znojmo, 24 - Povo/Trento</t>
+          <t>SSPG – via Circonvallazione, 44 – Tione</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IC TRENTO 2</t>
+          <t>IC TRENTO 1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SSPG - Via Ponte Alto, 2/1 - Cognola/Trento</t>
+          <t>SSPG - via Znojmo, 24 - Povo/Trento</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IC TRENTO 3</t>
+          <t>IC TRENTO 2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Via Vittorio Veneto 61 - Trento</t>
+          <t>SSPG - Via Ponte Alto, 2/1 - Cognola/Trento</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IC TRENTO 4</t>
+          <t>IC TRENTO 3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Piazzale CHIESA SACRO CUORE - Viale Verona 143 – Trento</t>
+          <t>Via Vittorio Veneto 61 - Trento</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IC TRENTO 5</t>
+          <t>IC TRENTO 4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Funivia Trento/Sardagna - Trento</t>
+          <t>Piazzale CHIESA SACRO CUORE - Viale Verona 143 – Trento</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -946,7 +946,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IC TRENTO 6</t>
+          <t>IC TRENTO 5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -955,18 +955,18 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IC TRENTO 7</t>
+          <t>IC TRENTO 6</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SSPG - via 4 Novembre, 35/1 - Gardolo/Trento</t>
+          <t>Funivia Trento/Sardagna - Trento</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -976,12 +976,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC TRENTO 7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SSPG – Via della Pace 10 - Pinzolo</t>
+          <t>SSPG - via 4 Novembre, 35/1 - Gardolo/Trento</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -991,16 +991,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IC VALLE DEI LAGHI-DRO</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fermata bus c/o farmacia - via Roma - Vezzano</t>
+          <t>SSPG – Via della Pace 10 - Pinzolo</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Piazza Italia - Cavedine</t>
+          <t>Fermata bus c/o farmacia - via Roma - Vezzano</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SSPG DRO - Parcheggio Scuole Nuove - Dro</t>
+          <t>Piazza Italia - Cavedine</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IC VALLE DI LEDRO</t>
+          <t>IC VALLE DEI LAGHI-DRO</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Via Falcone e Borsellino - Bezzecca</t>
+          <t>SSPG DRO - Parcheggio Scuole Nuove - Dro</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1051,12 +1051,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IC VIGOLO VATTARO</t>
+          <t>IC VALLE DI LEDRO</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fermata bus – Vigolo Vattaro</t>
+          <t>Via Falcone e Borsellino - Bezzecca</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1066,15 +1066,30 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>IC VIGOLO VATTARO</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Fermata bus – Vigolo Vattaro</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>IS MARTINO MARTINI MEZZOLOMBARDO – Students Staff</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Via Perlasca 4 - Mezzolombardo</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C45" t="n">
         <v>22</v>
       </c>
     </row>

--- a/tests/realSuite/Piano-Viaggi_Atletica-Ragazz-_8-maggio-2025_def_con-cell/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Atletica-Ragazz-_8-maggio-2025_def_con-cell/input.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Piazzale Scuola primaria – Via Betta - Ala</t>
+          <t>Scuola primaria "Abramo Betta", 9, Via Abramo Betta, Ala, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38061, Italia</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/tests/realSuite/Piano-Viaggi_Atletica-Ragazz-_8-maggio-2025_def_con-cell/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Atletica-Ragazz-_8-maggio-2025_def_con-cell/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,312 +451,312 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC ALDENO-MATTARELLO</t>
+          <t>IC ALTOPIANO DI PINE'</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fermata Bus "Al Parco" - Via Torre Franca - Mattarello</t>
+          <t>Scuola Media "don Tarter", 6, Via del 26 maggio, Gardizzola, Marini, Miola, Baselga di Piné, Comunità Alta Valsugana e Bersntol, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38057, Italia</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC ALDENO-MATTARELLO</t>
+          <t>IC BASSA ANAUNIA-TUENNO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fermata bus – via Filzi - Aldeno</t>
+          <t>Via Colle Verde 3 - Denno</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC ALTOPIANO DI PINE'</t>
+          <t>IC BASSA ANAUNIA-TUENNO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Via del 26 Maggio - Baselga di Pinè</t>
+          <t>Via Maistrelli, 11, Ville d'Anaunia fr. Tuenno</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC AVIO</t>
+          <t>IC BORGO VALSUGANA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Via De Gasperi 69 - Avio</t>
+          <t>Via Spagnolla 1 – Borgo Valsugana</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC BASSA ANAUNIA-TUENNO</t>
+          <t>IC CAVALESE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Via Colle Verde 3 - Denno</t>
+          <t>SSPG – Fermata bus – Piazza Verdi - Cavalese</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC BASSA ANAUNIA-TUENNO</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Via Maistrelli, 11, Ville d'Anaunia fr. Tuenno</t>
+          <t>SSPG Cembra - Via Negritelle, 1 - Cembra</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC BORGO VALSUGANA</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Via Spagnolla 1 – Borgo Valsugana</t>
+          <t>SSPG Giovo - Via Grec 2 - Giovo</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC CAVALESE</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SSPG – Fermata bus – Piazza Verdi - Cavalese</t>
+          <t>SSPG Segonzano - Loc. Scancio 69 - Segonzano</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC CEMBRA</t>
+          <t>IC CHIESE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SSPG Cembra - Via Negritelle, 1 - Cembra</t>
+          <t>Via Fiera 1 – Pieve di Bono</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC CEMBRA</t>
+          <t>IC CHIESE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SSPG Giovo - Via Grec 2 - Giovo</t>
+          <t>Via Papaleoni 5 - Storo</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC CEMBRA</t>
+          <t>IC FOLGARIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SSPG Segonzano - Loc. Scancio 69 - Segonzano</t>
+          <t>Fermata bus Palaghiaccio - Folgaria</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC CHIESE</t>
+          <t>IC FONDO-REVO'</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Via Fiera 1 – Pieve di Bono</t>
+          <t>Park autobus c/o Vigili Fuoco Volontari - Revò</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC CHIESE</t>
+          <t>IC FONDO-REVO'</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Via Papaleoni 5 - Storo</t>
+          <t>SSPG - via G. Garibaldi, 24 - Fondo</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC FOLGARIA</t>
+          <t>IC ISERA/ROVERETO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fermata bus Palaghiaccio - Folgaria</t>
+          <t>Viale Vittoria 43 - Rovereto</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC FONDO-REVO'</t>
+          <t>IC LAVIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Park autobus c/o Vigili Fuoco Volontari - Revò</t>
+          <t>SSPG - via Carlo Sette, 13/a - Lavis</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC FONDO-REVO'</t>
+          <t>IC LEVICO TERME</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SSPG - via G. Garibaldi, 24 - Fondo</t>
+          <t>SSPG – via della Pace, 5 - Levico Terme</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC ISERA/ROVERETO</t>
+          <t>IC MEZZANO SANTA CROCE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Viale Vittoria 43 - Rovereto</t>
+          <t>Via Molaren, 29 - Mezzano</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC LAVIS</t>
+          <t>IC MEZZOCORONA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SSPG - via Carlo Sette, 13/a - Lavis</t>
+          <t>Via Fornai, 1 - Mezzocorona</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC LEVICO TERME</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SSPG – via della Pace, 5 - Levico Terme</t>
+          <t>Via Trento Fermata bus - Spormaggiore</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC MEZZANO SANTA CROCE</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Via Molaren, 29 - Mezzano</t>
+          <t>Via degli Alpini, 17 - Mezzolombardo</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC MEZZOCORONA</t>
+          <t>IC PERGINE 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Via Fornai, 1 - Mezzocorona</t>
+          <t>SSPG – Via Caduti, 39 - Pergine Valsugana</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -766,72 +766,72 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC RIVA 1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Via Trento Fermata bus - Spormaggiore</t>
+          <t>SSPG - via D. Chiesa, 10 - Riva del Garda</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC RIVA 2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Via degli Alpini, 17 - Mezzolombardo</t>
+          <t>Centro sportivo "Malossini" – Via Ginestre 1 - Riva del Garda</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC PERGINE 1</t>
+          <t>IC TAIO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SSPG – Via Caduti, 39 - Pergine Valsugana</t>
+          <t>Piazza della Chiesa - Coredo</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IC RIVA 1</t>
+          <t>IC TAIO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SSPG - via D. Chiesa, 10 - Riva del Garda</t>
+          <t>Piazza della Chiesa – Taio</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IC RIVA 2</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Centro sportivo "Malossini" – Via Ginestre 1 - Riva del Garda</t>
+          <t>SSPG – via Circonvallazione, 44 – Tione</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -841,57 +841,57 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC TRENTO 1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Piazza della Chiesa - Coredo</t>
+          <t>SSPG - via Znojmo, 24 - Povo/Trento</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IC TAIO</t>
+          <t>IC TRENTO 2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Piazza della Chiesa – Taio</t>
+          <t>SSPG - Via Ponte Alto, 2/1 - Cognola/Trento</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC TRENTO 3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SSPG – via Circonvallazione, 44 – Tione</t>
+          <t>Via Vittorio Veneto 61 - Trento</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IC TRENTO 1</t>
+          <t>IC TRENTO 4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SSPG - via Znojmo, 24 - Povo/Trento</t>
+          <t>Piazzale CHIESA SACRO CUORE - Viale Verona 143 – Trento</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -901,102 +901,102 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IC TRENTO 2</t>
+          <t>IC TRENTO 5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SSPG - Via Ponte Alto, 2/1 - Cognola/Trento</t>
+          <t>Funivia Trento/Sardagna - Trento</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IC TRENTO 3</t>
+          <t>IC TRENTO 6</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Via Vittorio Veneto 61 - Trento</t>
+          <t>Funivia Trento/Sardagna - Trento</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IC TRENTO 4</t>
+          <t>IC TRENTO 7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Piazzale CHIESA SACRO CUORE - Viale Verona 143 – Trento</t>
+          <t>SSPG - via 4 Novembre, 35/1 - Gardolo/Trento</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IC TRENTO 5</t>
+          <t>IC VAL RENDENA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Funivia Trento/Sardagna - Trento</t>
+          <t>SSPG – Via della Pace 10 - Pinzolo</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IC TRENTO 6</t>
+          <t>IC VALLE DEI LAGHI-DRO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Funivia Trento/Sardagna - Trento</t>
+          <t>Fermata bus c/o farmacia - via Roma - Vezzano</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IC TRENTO 7</t>
+          <t>IC VALLE DEI LAGHI-DRO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SSPG - via 4 Novembre, 35/1 - Gardolo/Trento</t>
+          <t>Piazza Italia - Cavedine</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IC VAL RENDENA</t>
+          <t>IC VALLE DEI LAGHI-DRO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SSPG – Via della Pace 10 - Pinzolo</t>
+          <t>SSPG DRO - Parcheggio Scuole Nuove - Dro</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1006,90 +1006,45 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IC VALLE DEI LAGHI-DRO</t>
+          <t>IC VALLE DI LEDRO</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fermata bus c/o farmacia - via Roma - Vezzano</t>
+          <t>Via Falcone e Borsellino - Bezzecca</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IC VALLE DEI LAGHI-DRO</t>
+          <t>IC VIGOLO VATTARO</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Piazza Italia - Cavedine</t>
+          <t>Fermata bus – Vigolo Vattaro</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IC VALLE DEI LAGHI-DRO</t>
+          <t>IS MARTINO MARTINI MEZZOLOMBARDO – Students Staff</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SSPG DRO - Parcheggio Scuole Nuove - Dro</t>
+          <t>Via Perlasca 4 - Mezzolombardo</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>IC VALLE DI LEDRO</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Via Falcone e Borsellino - Bezzecca</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>IC VIGOLO VATTARO</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Fermata bus – Vigolo Vattaro</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>IS MARTINO MARTINI MEZZOLOMBARDO – Students Staff</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Via Perlasca 4 - Mezzolombardo</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
         <v>22</v>
       </c>
     </row>
